--- a/Labs/Lab06/Lab6Rubric_CS295N.xlsx
+++ b/Labs/Lab06/Lab6Rubric_CS295N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/birdb/Projects/CS295N-CourseMaterials/Labs/Lab06/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DataCard/Repos/CS295N-Repos/CS295N-CourseMaterials/Labs/Lab06/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA03845-CABE-B746-944A-7B5359A4BAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AEA874-709F-D240-8C21-943103E2FC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16300" yWindow="500" windowWidth="12500" windowHeight="16500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10620" yWindow="540" windowWidth="15620" windowHeight="15460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lab3Rubric_CS295N" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="32">
   <si>
     <t>-----------------------------------</t>
   </si>
@@ -124,13 +124,19 @@
   </si>
   <si>
     <t>Used correct style</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Option A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -315,6 +321,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -661,7 +675,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -681,6 +695,13 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -740,9 +761,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -780,7 +801,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -886,7 +907,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1028,7 +1049,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1553,6 +1574,9 @@
       <c r="C6" t="s">
         <v>1</v>
       </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="18">
       <c r="A7" t="s">
@@ -1564,20 +1588,28 @@
       <c r="C7">
         <v>10</v>
       </c>
+      <c r="D7" s="13" t="s">
+        <v>31</v>
+      </c>
       <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="D9" s="13"/>
       <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="D10" s="13"/>
+    </row>
+    <row r="11" spans="1:6" ht="17">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1587,6 +1619,9 @@
       <c r="C11" s="12">
         <v>5</v>
       </c>
+      <c r="D11" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6">
@@ -1598,6 +1633,9 @@
       </c>
       <c r="C12" s="12">
         <v>5</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1610,6 +1648,9 @@
       <c r="C13" s="12">
         <v>5</v>
       </c>
+      <c r="D13" s="13" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
@@ -1621,16 +1662,23 @@
       <c r="C14">
         <v>10</v>
       </c>
+      <c r="D14" s="13" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="A15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B15">
-        <v>10</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
+      <c r="B15" s="15">
+        <f>10-10</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1639,22 +1687,25 @@
       </c>
       <c r="B16" s="3">
         <f>SUM(B11:B15)</f>
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3">
         <f>SUM(C11:C15)</f>
-        <v>35</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
+      <c r="D17" s="13"/>
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="D18" s="13"/>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6">
@@ -1667,6 +1718,9 @@
       <c r="C19">
         <v>3</v>
       </c>
+      <c r="D19" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6">
@@ -1679,6 +1733,9 @@
       <c r="C20">
         <v>2</v>
       </c>
+      <c r="D20" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6">
@@ -1693,10 +1750,12 @@
         <f>SUM(C19:C20)</f>
         <v>5</v>
       </c>
+      <c r="D21" s="13"/>
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1"/>
+      <c r="D22" s="13"/>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6">
@@ -1705,31 +1764,39 @@
       </c>
       <c r="B23" s="10">
         <f>SUM(B7,B16,B21)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C23" s="10">
         <f>SUM(C7,C16,C21)</f>
-        <v>50</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D23" s="13"/>
       <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6">
+      <c r="D24" s="13"/>
       <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6">
+      <c r="D25" s="13"/>
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D26" s="13"/>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
+      <c r="D27" s="13"/>
       <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="D28" s="13"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="4" t="s">
@@ -1741,6 +1808,9 @@
       <c r="C29" t="s">
         <v>1</v>
       </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6">
@@ -1753,20 +1823,24 @@
       <c r="C30">
         <v>10</v>
       </c>
+      <c r="D30" s="13"/>
     </row>
     <row r="31" spans="1:6">
+      <c r="D31" s="13"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="D32" s="13"/>
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>8</v>
       </c>
+      <c r="D33" s="13"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
@@ -1778,6 +1852,7 @@
       <c r="C34">
         <v>5</v>
       </c>
+      <c r="D34" s="13"/>
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6">
@@ -1790,6 +1865,7 @@
       <c r="C35">
         <v>5</v>
       </c>
+      <c r="D35" s="13"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
@@ -1801,6 +1877,7 @@
       <c r="C36" s="12">
         <v>5</v>
       </c>
+      <c r="D36" s="13"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
@@ -1812,6 +1889,7 @@
       <c r="C37">
         <v>10</v>
       </c>
+      <c r="D37" s="13"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
@@ -1823,6 +1901,7 @@
       <c r="C38">
         <v>10</v>
       </c>
+      <c r="D38" s="13"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="7" t="s">
@@ -1836,15 +1915,18 @@
         <f>SUM(C34:C38)</f>
         <v>35</v>
       </c>
+      <c r="D39" s="13"/>
     </row>
     <row r="40" spans="1:6">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
+      <c r="D40" s="13"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="D41" s="13"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
@@ -1856,6 +1938,7 @@
       <c r="C42">
         <v>3</v>
       </c>
+      <c r="D42" s="13"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
@@ -1867,6 +1950,7 @@
       <c r="C43">
         <v>2</v>
       </c>
+      <c r="D43" s="13"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
@@ -1880,9 +1964,11 @@
         <f>SUM(C42:C43)</f>
         <v>5</v>
       </c>
+      <c r="D44" s="13"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1"/>
+      <c r="D45" s="13"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="9" t="s">
@@ -1896,26 +1982,34 @@
         <f>SUM(C30,C39,C44)</f>
         <v>50</v>
       </c>
+      <c r="D46" s="13"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1"/>
+      <c r="D47" s="13"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="D48" s="13"/>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="D49" s="13"/>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D50" s="13"/>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="D51" s="13"/>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="4" t="s">
         <v>19</v>
       </c>
@@ -1925,8 +2019,11 @@
       <c r="C52" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -1936,20 +2033,26 @@
       <c r="C53">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" s="4" customFormat="1">
+      <c r="D53" s="13"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="D54" s="13"/>
+    </row>
+    <row r="55" spans="1:4" s="4" customFormat="1">
       <c r="A55" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B55"/>
       <c r="C55"/>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="D55" s="14"/>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="D56" s="13"/>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -1959,8 +2062,9 @@
       <c r="C57">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="D57" s="13"/>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -1970,8 +2074,9 @@
       <c r="C58">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58" s="13"/>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>27</v>
       </c>
@@ -1981,8 +2086,9 @@
       <c r="C59">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="D59" s="13"/>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -1992,8 +2098,9 @@
       <c r="C60">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="D60" s="13"/>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>24</v>
       </c>
@@ -2003,8 +2110,9 @@
       <c r="C61">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="D61" s="13"/>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" s="7" t="s">
         <v>4</v>
       </c>
@@ -2016,17 +2124,20 @@
         <f>SUM(C57:C61)</f>
         <v>35</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="D62" s="13"/>
+    </row>
+    <row r="63" spans="1:4">
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="D63" s="13"/>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="D64" s="13"/>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -2036,8 +2147,9 @@
       <c r="C65">
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65" s="13"/>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>29</v>
       </c>
@@ -2047,8 +2159,9 @@
       <c r="C66">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66" s="13"/>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
         <v>4</v>
       </c>
@@ -2060,11 +2173,13 @@
         <f>SUM(C65:C66)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67" s="13"/>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" s="1"/>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="D68" s="13"/>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" s="9" t="s">
         <v>3</v>
       </c>
@@ -2076,8 +2191,10 @@
         <f>SUM(C53,C62,C67)</f>
         <v>50</v>
       </c>
+      <c r="D69" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Labs/Lab06/Lab6Rubric_CS295N.xlsx
+++ b/Labs/Lab06/Lab6Rubric_CS295N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DataCard/Repos/CS295N-Repos/CS295N-CourseMaterials/Labs/Lab06/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\CS295N-296N-Repos\CS295N-CourseMaterials\Labs\Lab06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AEA874-709F-D240-8C21-943103E2FC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B4A3EE-7C1D-4E30-B3F9-F2D4AC2B03F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10620" yWindow="540" windowWidth="15620" windowHeight="15460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15060" yWindow="4200" windowWidth="15048" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lab3Rubric_CS295N" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="35">
   <si>
     <t>-----------------------------------</t>
   </si>
@@ -120,9 +120,6 @@
     <t>A page showing all comments</t>
   </si>
   <si>
-    <t>Good start.</t>
-  </si>
-  <si>
     <t>Used correct style</t>
   </si>
   <si>
@@ -130,6 +127,18 @@
   </si>
   <si>
     <t>Option A</t>
+  </si>
+  <si>
+    <t>Part A, MVC Movie Tutorial</t>
+  </si>
+  <si>
+    <t>Exercise: Report (A, B, C) with screen-shot</t>
+  </si>
+  <si>
+    <t>Not required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excellent work! Good job of adding a database! </t>
   </si>
 </sst>
 </file>
@@ -675,7 +684,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -698,10 +707,28 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1058,12 +1085,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="44.33203125" customWidth="1"/>
+    <col min="1" max="1" width="44.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19">
+    <row r="1" spans="1:6" ht="18">
       <c r="A1" s="5" t="s">
         <v>16</v>
       </c>
@@ -1086,7 +1113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18">
+    <row r="5" spans="1:6" ht="17.399999999999999">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1183,7 +1210,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -1327,7 +1354,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -1490,7 +1517,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -1536,12 +1563,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C8BAC4-7C35-B64C-9C0F-AC9B3324E891}">
   <dimension ref="A1:F69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="44.33203125" customWidth="1"/>
+    <col min="1" max="1" width="44.296875" customWidth="1"/>
+    <col min="2" max="2" width="7.19921875" customWidth="1"/>
+    <col min="3" max="3" width="5.8984375" customWidth="1"/>
+    <col min="4" max="4" width="17.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19">
+    <row r="1" spans="1:6" ht="18">
       <c r="A1" s="5" t="s">
         <v>16</v>
       </c>
@@ -1557,16 +1587,19 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:6">
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -1578,28 +1611,32 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18">
+    <row r="7" spans="1:6" ht="17.399999999999999">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
+        <v>32</v>
+      </c>
+      <c r="B7" s="17">
+        <v>10</v>
+      </c>
+      <c r="C7" s="17">
         <v>10</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="13"/>
       <c r="F9" s="6"/>
     </row>
@@ -1607,20 +1644,22 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:6" ht="17">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="12">
-        <v>5</v>
-      </c>
-      <c r="C11" s="12">
+      <c r="B11" s="18">
+        <v>5</v>
+      </c>
+      <c r="C11" s="18">
         <v>5</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="6"/>
     </row>
@@ -1628,76 +1667,76 @@
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="12">
-        <v>5</v>
-      </c>
-      <c r="C12" s="12">
+      <c r="B12" s="18">
+        <v>5</v>
+      </c>
+      <c r="C12" s="18">
         <v>5</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="12">
-        <v>5</v>
-      </c>
-      <c r="C13" s="12">
+      <c r="B13" s="18">
+        <v>5</v>
+      </c>
+      <c r="C13" s="18">
         <v>5</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B14">
-        <v>10</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="17">
+        <v>10</v>
+      </c>
+      <c r="C14" s="17">
         <v>10</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="19">
         <f>10-10</f>
         <v>0</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="19">
         <v>0</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="20">
         <f>SUM(B11:B15)</f>
         <v>25</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="20">
         <f>SUM(C11:C15)</f>
         <v>25</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="13"/>
       <c r="F17" s="6"/>
     </row>
@@ -1705,6 +1744,8 @@
       <c r="A18" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="13"/>
       <c r="F18" s="6"/>
     </row>
@@ -1712,29 +1753,29 @@
       <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="17">
         <v>3</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="17">
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="17">
+        <v>2</v>
+      </c>
+      <c r="C20" s="17">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>30</v>
       </c>
       <c r="F20" s="6"/>
     </row>
@@ -1742,11 +1783,11 @@
       <c r="A21" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="20">
         <f>SUM(B19:B20)</f>
         <v>5</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="20">
         <f>SUM(C19:C20)</f>
         <v>5</v>
       </c>
@@ -1755,6 +1796,8 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
       <c r="D22" s="13"/>
       <c r="F22" s="6"/>
     </row>
@@ -1762,11 +1805,11 @@
       <c r="A23" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="21">
         <f>SUM(B7,B16,B21)</f>
         <v>40</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="21">
         <f>SUM(C7,C16,C21)</f>
         <v>40</v>
       </c>
@@ -1789,10 +1832,12 @@
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="13"/>
+      <c r="A27" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
       <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6">
@@ -1815,17 +1860,21 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30">
-        <v>10</v>
-      </c>
-      <c r="C30">
-        <v>10</v>
-      </c>
-      <c r="D30" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="B30" s="17">
+        <v>10</v>
+      </c>
+      <c r="C30" s="17">
+        <v>10</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
       <c r="D31" s="13"/>
       <c r="F31" s="6"/>
     </row>
@@ -1833,6 +1882,8 @@
       <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
       <c r="D32" s="13"/>
       <c r="F32" s="6"/>
     </row>
@@ -1840,127 +1891,141 @@
       <c r="A33" t="s">
         <v>8</v>
       </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
       <c r="D33" s="13"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>22</v>
       </c>
-      <c r="B34">
-        <v>5</v>
-      </c>
-      <c r="C34">
-        <v>5</v>
-      </c>
-      <c r="D34" s="13"/>
+      <c r="B34" s="17">
+        <v>5</v>
+      </c>
+      <c r="C34" s="17">
+        <v>5</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>14</v>
       </c>
-      <c r="B35">
-        <v>5</v>
-      </c>
-      <c r="C35">
-        <v>5</v>
-      </c>
-      <c r="D35" s="13"/>
+      <c r="B35" s="17">
+        <v>5</v>
+      </c>
+      <c r="C35" s="17">
+        <v>5</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="12">
-        <v>5</v>
-      </c>
-      <c r="C36" s="12">
-        <v>5</v>
-      </c>
-      <c r="D36" s="13"/>
+      <c r="B36" s="18">
+        <v>5</v>
+      </c>
+      <c r="C36" s="18">
+        <v>5</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>23</v>
       </c>
-      <c r="B37">
-        <v>10</v>
-      </c>
-      <c r="C37">
-        <v>10</v>
-      </c>
-      <c r="D37" s="13"/>
+      <c r="B37" s="17">
+        <v>10</v>
+      </c>
+      <c r="C37" s="17">
+        <v>10</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" t="s">
+      <c r="A38" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B38">
-        <v>10</v>
-      </c>
-      <c r="C38">
-        <v>10</v>
-      </c>
-      <c r="D38" s="13"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="13" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="20">
         <f>SUM(B34:B38)</f>
-        <v>35</v>
-      </c>
-      <c r="C39" s="3">
+        <v>25</v>
+      </c>
+      <c r="C39" s="20">
         <f>SUM(C34:C38)</f>
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D39" s="13"/>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="13"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
       <c r="D41" s="13"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>7</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="17">
         <v>3</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="17">
         <v>3</v>
       </c>
-      <c r="D42" s="13"/>
+      <c r="D42" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="17">
+        <v>2</v>
+      </c>
+      <c r="C43" s="17">
+        <v>2</v>
+      </c>
+      <c r="D43" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B43">
-        <v>2</v>
-      </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-      <c r="D43" s="13"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="20">
         <f>SUM(B42:B43)</f>
         <v>5</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="20">
         <f>SUM(C42:C43)</f>
         <v>5</v>
       </c>
@@ -1968,19 +2033,21 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
       <c r="D45" s="13"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="21">
         <f>SUM(B30,B39,B44)</f>
-        <v>50</v>
-      </c>
-      <c r="C46" s="10">
+        <v>40</v>
+      </c>
+      <c r="C46" s="21">
         <f>SUM(C30,C39,C44)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D46" s="13"/>
     </row>
@@ -2001,10 +2068,12 @@
       <c r="D49" s="13"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="13"/>
+      <c r="A50" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
     </row>
     <row r="51" spans="1:4">
       <c r="D51" s="13"/>
@@ -2025,151 +2094,173 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53">
-        <v>10</v>
-      </c>
-      <c r="C53">
-        <v>10</v>
-      </c>
-      <c r="D53" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="B53" s="17">
+        <v>10</v>
+      </c>
+      <c r="C53" s="17">
+        <v>10</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="54" spans="1:4">
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
       <c r="D54" s="13"/>
     </row>
     <row r="55" spans="1:4" s="4" customFormat="1">
       <c r="A55" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55" s="14"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="13"/>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>8</v>
       </c>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
       <c r="D56" s="13"/>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>15</v>
       </c>
-      <c r="B57">
-        <v>5</v>
-      </c>
-      <c r="C57">
-        <v>5</v>
-      </c>
-      <c r="D57" s="13"/>
+      <c r="B57" s="17">
+        <v>5</v>
+      </c>
+      <c r="C57" s="17">
+        <v>5</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>18</v>
       </c>
-      <c r="B58">
-        <v>5</v>
-      </c>
-      <c r="C58">
-        <v>5</v>
-      </c>
-      <c r="D58" s="13"/>
+      <c r="B58" s="17">
+        <v>5</v>
+      </c>
+      <c r="C58" s="17">
+        <v>5</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>27</v>
       </c>
-      <c r="B59">
-        <v>5</v>
-      </c>
-      <c r="C59">
-        <v>5</v>
-      </c>
-      <c r="D59" s="13"/>
+      <c r="B59" s="17">
+        <v>5</v>
+      </c>
+      <c r="C59" s="17">
+        <v>5</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>23</v>
       </c>
-      <c r="B60">
-        <v>10</v>
-      </c>
-      <c r="C60">
-        <v>10</v>
-      </c>
-      <c r="D60" s="13"/>
+      <c r="B60" s="17">
+        <v>10</v>
+      </c>
+      <c r="C60" s="17">
+        <v>10</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" t="s">
+      <c r="A61" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B61">
-        <v>10</v>
-      </c>
-      <c r="C61">
-        <v>10</v>
-      </c>
-      <c r="D61" s="13"/>
+      <c r="B61" s="19">
+        <v>0</v>
+      </c>
+      <c r="C61" s="19">
+        <v>0</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="20">
         <f>SUM(B57:B61)</f>
-        <v>35</v>
-      </c>
-      <c r="C62" s="3">
+        <v>25</v>
+      </c>
+      <c r="C62" s="20">
         <f>SUM(C57:C61)</f>
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D62" s="13"/>
     </row>
     <row r="63" spans="1:4">
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
       <c r="D63" s="13"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
       <c r="D64" s="13"/>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>7</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="17">
         <v>3</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="17">
         <v>3</v>
       </c>
-      <c r="D65" s="13"/>
+      <c r="D65" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" s="17">
+        <v>2</v>
+      </c>
+      <c r="C66" s="17">
+        <v>2</v>
+      </c>
+      <c r="D66" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66">
-        <v>2</v>
-      </c>
-      <c r="D66" s="13"/>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="20">
         <f>SUM(B65:B66)</f>
         <v>5</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="20">
         <f>SUM(C65:C66)</f>
         <v>5</v>
       </c>
@@ -2177,24 +2268,31 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
       <c r="D68" s="13"/>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="21">
         <f>SUM(B53,B62,B67)</f>
-        <v>50</v>
-      </c>
-      <c r="C69" s="10">
+        <v>40</v>
+      </c>
+      <c r="C69" s="21">
         <f>SUM(C53,C62,C67)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D69" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A50:D50"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Labs/Lab06/Lab6Rubric_CS295N.xlsx
+++ b/Labs/Lab06/Lab6Rubric_CS295N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\CS295N-296N-Repos\CS295N-CourseMaterials\Labs\Lab06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B4A3EE-7C1D-4E30-B3F9-F2D4AC2B03F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C40CD4-219A-414F-8C81-6D9F390032D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15060" yWindow="4200" windowWidth="15048" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15060" yWindow="4200" windowWidth="15048" windowHeight="12960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lab3Rubric_CS295N" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="36">
   <si>
     <t>-----------------------------------</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t xml:space="preserve">Excellent work! Good job of adding a database! </t>
+  </si>
+  <si>
+    <t>Here's the grade breakdown:</t>
   </si>
 </sst>
 </file>
@@ -684,7 +687,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -708,12 +711,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
@@ -728,6 +725,18 @@
     </xf>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1562,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C8BAC4-7C35-B64C-9C0F-AC9B3324E891}">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="44.296875" customWidth="1"/>
@@ -1587,236 +1596,278 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:6" ht="20.399999999999999" customHeight="1">
+      <c r="A6" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="17.399999999999999">
-      <c r="A7" t="s">
+      <c r="E7" s="13"/>
+    </row>
+    <row r="8" spans="1:6" ht="17.399999999999999">
+      <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="17">
-        <v>10</v>
-      </c>
-      <c r="C7" s="17">
-        <v>10</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="B8" s="15">
+        <v>10</v>
+      </c>
+      <c r="C8" s="15">
+        <v>10</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="13"/>
+      <c r="E8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="13"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
       <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="18">
-        <v>5</v>
-      </c>
-      <c r="C11" s="18">
-        <v>5</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="18">
-        <v>5</v>
-      </c>
-      <c r="C12" s="18">
+        <v>9</v>
+      </c>
+      <c r="B12" s="16">
+        <v>5</v>
+      </c>
+      <c r="C12" s="16">
         <v>5</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>29</v>
       </c>
+      <c r="E12" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="18">
-        <v>5</v>
-      </c>
-      <c r="C13" s="18">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16">
+        <v>5</v>
+      </c>
+      <c r="C13" s="16">
         <v>5</v>
       </c>
       <c r="D13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="16">
+        <v>5</v>
+      </c>
+      <c r="C14" s="16">
+        <v>5</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="17">
-        <v>10</v>
-      </c>
-      <c r="C14" s="17">
-        <v>10</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="14" t="s">
+      <c r="B15" s="15">
+        <v>10</v>
+      </c>
+      <c r="C15" s="15">
+        <v>10</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="31.2">
+      <c r="A16" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B16" s="17">
         <f>10-10</f>
         <v>0</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C16" s="17">
         <v>0</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D16" s="13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="E16" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="20">
-        <f>SUM(B11:B15)</f>
+      <c r="B17" s="18">
+        <f>SUM(B12:B16)</f>
         <v>25</v>
       </c>
-      <c r="C16" s="20">
-        <f>SUM(C11:C15)</f>
+      <c r="C17" s="18">
+        <f>SUM(C12:C16)</f>
         <v>25</v>
       </c>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
       <c r="D17" s="13"/>
-      <c r="F17" s="6"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="13"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="17">
-        <v>3</v>
-      </c>
-      <c r="C19" s="17">
-        <v>3</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>29</v>
-      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="15">
+        <v>3</v>
+      </c>
+      <c r="C20" s="15">
+        <v>3</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B21" s="15">
         <v>2</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C21" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
+      <c r="D21" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="20">
-        <f>SUM(B19:B20)</f>
-        <v>5</v>
-      </c>
-      <c r="C21" s="20">
-        <f>SUM(C19:C20)</f>
-        <v>5</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="B22" s="18">
+        <f>SUM(B20:B21)</f>
+        <v>5</v>
+      </c>
+      <c r="C22" s="18">
+        <f>SUM(C20:C21)</f>
+        <v>5</v>
+      </c>
       <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="1"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="21">
-        <f>SUM(B7,B16,B21)</f>
+      <c r="B24" s="19">
+        <f>SUM(B8,B17,B22)</f>
         <v>40</v>
       </c>
-      <c r="C23" s="21">
-        <f>SUM(C7,C16,C21)</f>
+      <c r="C24" s="19">
+        <f>SUM(C8,C17,C22)</f>
         <v>40</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6">
       <c r="D24" s="13"/>
       <c r="F24" s="6"/>
     </row>
@@ -1825,472 +1876,555 @@
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D26" s="13"/>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" ht="17.399999999999999" customHeight="1">
+      <c r="A28" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="D28" s="13"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="4" t="s">
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" ht="16.8" customHeight="1">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:6" ht="21.6" customHeight="1">
+      <c r="A30" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="13"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>2</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C31" t="s">
         <v>1</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D31" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="E31" s="13"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="17">
-        <v>10</v>
-      </c>
-      <c r="C30" s="17">
-        <v>10</v>
-      </c>
-      <c r="D30" s="13" t="s">
+      <c r="B32" s="15">
+        <v>10</v>
+      </c>
+      <c r="C32" s="15">
+        <v>10</v>
+      </c>
+      <c r="D32" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="13"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="4" t="s">
+      <c r="E32" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="13"/>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="13"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="17">
-        <v>5</v>
-      </c>
-      <c r="C34" s="17">
-        <v>5</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>29</v>
-      </c>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="17">
-        <v>5</v>
-      </c>
-      <c r="C35" s="17">
-        <v>5</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>29</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="18">
-        <v>5</v>
-      </c>
-      <c r="C36" s="18">
+        <v>22</v>
+      </c>
+      <c r="B36" s="15">
+        <v>5</v>
+      </c>
+      <c r="C36" s="15">
         <v>5</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>29</v>
       </c>
+      <c r="E36" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="6"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="15">
+        <v>5</v>
+      </c>
+      <c r="C37" s="15">
+        <v>5</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="16">
+        <v>5</v>
+      </c>
+      <c r="C38" s="16">
+        <v>5</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="17">
-        <v>10</v>
-      </c>
-      <c r="C37" s="17">
-        <v>10</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="14" t="s">
+      <c r="B39" s="15">
+        <v>10</v>
+      </c>
+      <c r="C39" s="15">
+        <v>10</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="31.2">
+      <c r="A40" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="13" t="s">
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="7" t="s">
+      <c r="E40" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="20">
-        <f>SUM(B34:B38)</f>
+      <c r="B41" s="18">
+        <f>SUM(B36:B40)</f>
         <v>25</v>
       </c>
-      <c r="C39" s="20">
-        <f>SUM(C34:C38)</f>
+      <c r="C41" s="18">
+        <f>SUM(C36:C40)</f>
         <v>25</v>
       </c>
-      <c r="D39" s="13"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="13"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="8" t="s">
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="13"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B44" s="15">
         <v>3</v>
       </c>
-      <c r="C42" s="17">
+      <c r="C44" s="15">
         <v>3</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
+      <c r="D44" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
         <v>28</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B45" s="15">
         <v>2</v>
       </c>
-      <c r="C43" s="17">
+      <c r="C45" s="15">
         <v>2</v>
       </c>
-      <c r="D43" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="2" t="s">
+      <c r="D45" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="20">
-        <f>SUM(B42:B43)</f>
-        <v>5</v>
-      </c>
-      <c r="C44" s="20">
-        <f>SUM(C42:C43)</f>
-        <v>5</v>
-      </c>
-      <c r="D44" s="13"/>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="1"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="13"/>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="21">
-        <f>SUM(B30,B39,B44)</f>
-        <v>40</v>
-      </c>
-      <c r="C46" s="21">
-        <f>SUM(C30,C39,C44)</f>
-        <v>40</v>
+      <c r="B46" s="18">
+        <f>SUM(B44:B45)</f>
+        <v>5</v>
+      </c>
+      <c r="C46" s="18">
+        <f>SUM(C44:C45)</f>
+        <v>5</v>
       </c>
       <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
       <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="2"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
+      <c r="A48" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="19">
+        <f>SUM(B32,B41,B46)</f>
+        <v>40</v>
+      </c>
+      <c r="C48" s="19">
+        <f>SUM(C32,C41,C46)</f>
+        <v>40</v>
+      </c>
       <c r="D48" s="13"/>
     </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:5">
+      <c r="A49" s="1"/>
+      <c r="D49" s="13"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="13"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="13"/>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="15" t="s">
+      <c r="D51" s="13"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="D51" s="13"/>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="4" t="s">
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="D53" s="13"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B54" t="s">
         <v>2</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C54" t="s">
         <v>1</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D54" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
+      <c r="E54" s="13"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="17">
-        <v>10</v>
-      </c>
-      <c r="C53" s="17">
-        <v>10</v>
-      </c>
-      <c r="D53" s="13" t="s">
+      <c r="B55" s="15">
+        <v>10</v>
+      </c>
+      <c r="C55" s="15">
+        <v>10</v>
+      </c>
+      <c r="D55" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="13"/>
-    </row>
-    <row r="55" spans="1:4" s="4" customFormat="1">
-      <c r="A55" s="4" t="s">
+      <c r="E55" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+    </row>
+    <row r="57" spans="1:5" s="4" customFormat="1">
+      <c r="A57" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="13"/>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
         <v>8</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="13"/>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
         <v>15</v>
       </c>
-      <c r="B57" s="17">
-        <v>5</v>
-      </c>
-      <c r="C57" s="17">
-        <v>5</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
+      <c r="B59" s="15">
+        <v>5</v>
+      </c>
+      <c r="C59" s="15">
+        <v>5</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
         <v>18</v>
       </c>
-      <c r="B58" s="17">
-        <v>5</v>
-      </c>
-      <c r="C58" s="17">
-        <v>5</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
+      <c r="B60" s="15">
+        <v>5</v>
+      </c>
+      <c r="C60" s="15">
+        <v>5</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
         <v>27</v>
       </c>
-      <c r="B59" s="17">
-        <v>5</v>
-      </c>
-      <c r="C59" s="17">
-        <v>5</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
+      <c r="B61" s="15">
+        <v>5</v>
+      </c>
+      <c r="C61" s="15">
+        <v>5</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="17">
-        <v>10</v>
-      </c>
-      <c r="C60" s="17">
-        <v>10</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="14" t="s">
+      <c r="B62" s="15">
+        <v>10</v>
+      </c>
+      <c r="C62" s="15">
+        <v>10</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="31.2">
+      <c r="A63" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B61" s="19">
+      <c r="B63" s="17">
         <v>0</v>
       </c>
-      <c r="C61" s="19">
+      <c r="C63" s="17">
         <v>0</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D63" s="13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="7" t="s">
+      <c r="E63" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B62" s="20">
-        <f>SUM(B57:B61)</f>
+      <c r="B64" s="18">
+        <f>SUM(B59:B63)</f>
         <v>25</v>
       </c>
-      <c r="C62" s="20">
-        <f>SUM(C57:C61)</f>
+      <c r="C64" s="18">
+        <f>SUM(C59:C63)</f>
         <v>25</v>
       </c>
-      <c r="D62" s="13"/>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="13"/>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="8" t="s">
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="13"/>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
         <v>7</v>
       </c>
-      <c r="B65" s="17">
+      <c r="B67" s="15">
         <v>3</v>
       </c>
-      <c r="C65" s="17">
+      <c r="C67" s="15">
         <v>3</v>
       </c>
-      <c r="D65" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
+      <c r="D67" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
         <v>28</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B68" s="15">
         <v>2</v>
       </c>
-      <c r="C66" s="17">
+      <c r="C68" s="15">
         <v>2</v>
       </c>
-      <c r="D66" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="2" t="s">
+      <c r="D68" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B67" s="20">
-        <f>SUM(B65:B66)</f>
-        <v>5</v>
-      </c>
-      <c r="C67" s="20">
-        <f>SUM(C65:C66)</f>
-        <v>5</v>
-      </c>
-      <c r="D67" s="13"/>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="1"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="13"/>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="9" t="s">
+      <c r="B69" s="18">
+        <f>SUM(B67:B68)</f>
+        <v>5</v>
+      </c>
+      <c r="C69" s="18">
+        <f>SUM(C67:C68)</f>
+        <v>5</v>
+      </c>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="1"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B69" s="21">
-        <f>SUM(B53,B62,B67)</f>
+      <c r="B71" s="19">
+        <f>SUM(B55,B64,B69)</f>
         <v>40</v>
       </c>
-      <c r="C69" s="21">
-        <f>SUM(C53,C62,C67)</f>
+      <c r="C71" s="19">
+        <f>SUM(C55,C64,C69)</f>
         <v>40</v>
       </c>
-      <c r="D69" s="13"/>
+      <c r="D71" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
